--- a/public/거래명세서양식.xlsx
+++ b/public/거래명세서양식.xlsx
@@ -2,22 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogleDrive\RPA 개발\05.Excel macro\2026_기연리프트\LM 용 CSV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\기연리프트자료_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{049FAA0C-594D-496F-9611-017313E305EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50113FB-1F8B-40DC-B44D-083A58E3AB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AEF61A8F-46C4-4D45-91AF-D953D59E8B92}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{50CEE825-8F2A-43ED-AB9B-230629EB0D8C}"/>
   </bookViews>
   <sheets>
-    <sheet name="거래명세서(유창)" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'거래명세서(유창)'!$B$15:$M$15</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,182 +36,295 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="70">
   <si>
     <t xml:space="preserve"> 거  래  명  세  표</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>(공급받는자 보관용)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>공  급  자</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>등록번호</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>138-81-83251</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>공 급 받 는 자</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>상호</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>주식회사 기연리프트</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>대표</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>이수용</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>주소</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>경기도 용인시 처인구 모현읍 갈담로112번길 21-3</t>
   </si>
   <si>
     <t>업태</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>사업지원 및             임대서비스업 외</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>종목</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>고소장비임대업 외</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>계약담당자</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>연락처</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>담당자</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>계산서담당자</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>이메일</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>giyeonlift@naver.com</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>공급내역</t>
   </si>
   <si>
     <t>작성일자</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>입금계좌</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>신한은행 140-010-007060 , 주식회사 기연리프트</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>순번</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>월</t>
-    <phoneticPr fontId="23" type="noConversion"/>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
     <t>일</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>품목</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>수량</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>단가</t>
-    <phoneticPr fontId="23" type="noConversion"/>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
     <t>공급가액</t>
-    <phoneticPr fontId="23" type="noConversion"/>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
     <t>부가세</t>
-    <phoneticPr fontId="23" type="noConversion"/>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
     <t>비고</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>공급가</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>\</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>부가세</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>합계</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>인수자</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>(인)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>현장담당자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>계산서메일</t>
+  </si>
+  <si>
+    <t>현장명</t>
+  </si>
+  <si>
+    <t>{사업자등록번호}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{고객명}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{대표자}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{주소}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{업태}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{종목}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{현장담당자}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{현장담당자연락처}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{계산서담당자}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{계산서담당자연락처}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{계산서이메일}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{현장명}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{월}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{일}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{품목} {청구기간}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{수량}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{렌탈료}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{공급가액}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{부가세}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{비고}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{공급가합계}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{부가세합계}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{총액}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{영업사원}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{영업사원연락처}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{청구담당자}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{청구담당자연락처}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="177" formatCode="&quot;₩&quot;#,##0"/>
     <numFmt numFmtId="178" formatCode="[$-412]AM/PM\ h:mm;@"/>
-    <numFmt numFmtId="179" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -226,6 +336,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
@@ -248,34 +365,13 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <u val="double"/>
-      <sz val="26"/>
-      <name val="굴림"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FF0070C0"/>
-      <name val="굴림"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="14"/>
       <name val="굴림"/>
       <family val="3"/>
       <charset val="129"/>
@@ -328,13 +424,6 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
-      <name val="굴림"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color rgb="FF0070C0"/>
       <name val="맑은 고딕"/>
@@ -350,13 +439,6 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="굴림"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
@@ -382,6 +464,14 @@
       <scheme val="major"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="15"/>
       <color rgb="FF0070C0"/>
       <name val="맑은 고딕"/>
@@ -396,14 +486,6 @@
       <charset val="129"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="15"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
@@ -412,24 +494,7 @@
       <scheme val="major"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="15"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -451,7 +516,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="44">
+  <borders count="46">
     <border>
       <left/>
       <right/>
@@ -998,6 +1063,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color rgb="FF0070C0"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FF0070C0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color rgb="FF0070C0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF0070C0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1006,480 +1097,453 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="31" fontId="9" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="31" fontId="7" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="38" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="19" fillId="2" borderId="38" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="41" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="43" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="2" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="31" fontId="12" fillId="2" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="31" fontId="12" fillId="2" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="31" fontId="10" fillId="2" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="31" fontId="10" fillId="2" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="31" fontId="10" fillId="2" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="31" fontId="12" fillId="2" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="13" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="14" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="13" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="41" fontId="12" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="12" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="31" fontId="14" fillId="2" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="31" fontId="14" fillId="2" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="31" fontId="12" fillId="2" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="31" fontId="12" fillId="2" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="31" fontId="12" fillId="2" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="31" fontId="14" fillId="2" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="38" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="22" fillId="2" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="22" fillId="2" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="22" fillId="2" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="22" fillId="2" borderId="38" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="22" fillId="2" borderId="38" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="2" borderId="38" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="22" fillId="2" borderId="38" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="22" fillId="2" borderId="39" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="25" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="25" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="25" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="25" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="41" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="25" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="25" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="25" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="25" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="19" fillId="2" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="19" fillId="2" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="19" fillId="2" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="19" fillId="2" borderId="38" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="2" borderId="38" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="19" fillId="2" borderId="38" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="19" fillId="2" borderId="39" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="21" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="21" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="21" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="21" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="21" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="21" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="21" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="21" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="25" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="25" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="25" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="25" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="25" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="21" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="21" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="21" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="21" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="21" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="2" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="2" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="2" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="12" fillId="2" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="43" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="2" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="2" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="2" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="2" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="2" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="2" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="15" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="28" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준_계약서 양식 2" xfId="2" xr:uid="{020DFE8D-3C4B-4A66-89EC-22F476CA07BE}"/>
+    <cellStyle name="표준_계약서 양식 2" xfId="2" xr:uid="{F8EE1EEA-E1FA-474C-BCA7-160FC13EFF18}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1514,7 +1578,7 @@
         <xdr:cNvPr id="2" name="AutoShape 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE19CFCE-D8E7-41E6-B534-67196A96A067}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E84711B-852D-47DA-90FA-EE62C7FC9FCB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1568,7 +1632,7 @@
         <xdr:cNvPr id="3" name="AutoShape 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DED0DB6-2A5C-402E-AB6E-AED6560F874D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{815EC159-EFC9-46A8-B68A-60EC9120C98A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1622,7 +1686,7 @@
         <xdr:cNvPr id="4" name="AutoShape 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FBA6D34B-831C-4165-8B2F-780EB32CCAD9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9112185B-801A-4CE0-9738-E1AF58663D5F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1676,7 +1740,7 @@
         <xdr:cNvPr id="5" name="AutoShape 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E7D7E24-E6AB-4EB2-83D0-4EB058F978B6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33596ACB-CD95-4C65-B39F-29F51E04F479}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1730,7 +1794,7 @@
         <xdr:cNvPr id="6" name="AutoShape 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33BD0143-1569-4467-BD74-840197A6557E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38D8BA1E-8065-449D-A723-CC356010754F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1784,7 +1848,7 @@
         <xdr:cNvPr id="7" name="AutoShape 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{939A6DAC-560D-46CD-8586-F27D2F07F5F0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A540491-F58C-4763-ABB6-3EB3A54821D8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1833,7 +1897,7 @@
         <xdr:cNvPr id="8" name="그림 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B3091B9-1ED9-436E-9373-85A8B13E0E55}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53844FFA-5579-43DF-98D5-2A2DCC18C1C5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1907,7 +1971,7 @@
         <xdr:cNvPr id="9" name="AutoShape 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81DDCDCD-786E-4944-9D0B-175B3AECBBFC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C0C4ADF-DD39-46A0-842B-05779275EFFC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1961,7 +2025,7 @@
         <xdr:cNvPr id="10" name="AutoShape 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EADFA292-4FD6-4774-958C-29F6239776B9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75C8D2E7-927B-45BD-A105-4A5056E79739}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2001,9 +2065,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2011,39 +2075,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -2095,7 +2159,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -2147,7 +2211,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2206,13 +2270,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -2221,6 +2278,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2285,22 +2349,39 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98B41A6B-1A20-45CD-9B85-0B7C8BC7A77E}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B1:V28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{499A9884-02AB-41E3-AC75-8EAF1925C5CB}">
+  <dimension ref="A1:U28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.75" customWidth="1"/>
@@ -2317,769 +2398,792 @@
     <col min="18" max="18" width="2.25" customWidth="1"/>
     <col min="19" max="19" width="7.25" customWidth="1"/>
     <col min="20" max="20" width="16.625" customWidth="1"/>
-    <col min="21" max="21" width="16.625" style="10" customWidth="1"/>
-    <col min="22" max="22" width="5.125" style="10" customWidth="1"/>
+    <col min="21" max="21" width="16.625" style="26" customWidth="1"/>
+    <col min="22" max="22" width="5.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="33.75" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:21" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="2"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
     </row>
-    <row r="2" spans="2:22" ht="33.75" x14ac:dyDescent="0.3">
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="2"/>
+    <row r="2" spans="1:21" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
     </row>
-    <row r="3" spans="2:22" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+    <row r="3" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="4"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="36"/>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="36"/>
+      <c r="R3" s="36"/>
+      <c r="S3" s="36"/>
+      <c r="T3" s="36"/>
+      <c r="U3" s="36"/>
     </row>
-    <row r="4" spans="2:22" ht="21" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="9"/>
+    <row r="4" spans="1:21" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="5"/>
     </row>
-    <row r="5" spans="2:22" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="11" t="s">
+    <row r="5" spans="1:21" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="14" t="s">
+      <c r="D5" s="41"/>
+      <c r="E5" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="11" t="s">
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="N5" s="13"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
-      <c r="S5" s="17"/>
-      <c r="T5" s="18"/>
-      <c r="U5" s="19"/>
-      <c r="V5" s="20"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="P5" s="45"/>
+      <c r="Q5" s="45"/>
+      <c r="R5" s="45"/>
+      <c r="S5" s="45"/>
+      <c r="T5" s="46"/>
+      <c r="U5" s="47"/>
     </row>
-    <row r="6" spans="2:22" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="21"/>
-      <c r="C6" s="22" t="s">
+    <row r="6" spans="1:21" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="38"/>
+      <c r="C6" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="24" t="s">
+      <c r="D6" s="31"/>
+      <c r="E6" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="24"/>
-      <c r="G6" s="25" t="s">
+      <c r="F6" s="48"/>
+      <c r="G6" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="26" t="s">
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="27"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="22" t="s">
+      <c r="K6" s="29"/>
+      <c r="L6" s="38"/>
+      <c r="M6" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="N6" s="23"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="23" t="s">
+      <c r="N6" s="31"/>
+      <c r="O6" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="P6" s="33"/>
+      <c r="Q6" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="R6" s="23"/>
-      <c r="S6" s="23"/>
-      <c r="T6" s="28"/>
-      <c r="U6" s="30"/>
-      <c r="V6" s="31"/>
+      <c r="R6" s="31"/>
+      <c r="S6" s="31"/>
+      <c r="T6" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="U6" s="34"/>
     </row>
-    <row r="7" spans="2:22" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="21"/>
-      <c r="C7" s="22" t="s">
+    <row r="7" spans="1:21" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="38"/>
+      <c r="C7" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="24" t="s">
+      <c r="D7" s="31"/>
+      <c r="E7" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="22" t="s">
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="32"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="N7" s="23"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="32"/>
-      <c r="Q7" s="32"/>
-      <c r="R7" s="32"/>
-      <c r="S7" s="32"/>
-      <c r="T7" s="32"/>
-      <c r="U7" s="30"/>
-      <c r="V7" s="31"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="P7" s="49"/>
+      <c r="Q7" s="49"/>
+      <c r="R7" s="49"/>
+      <c r="S7" s="49"/>
+      <c r="T7" s="49"/>
+      <c r="U7" s="34"/>
     </row>
-    <row r="8" spans="2:22" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="21"/>
-      <c r="C8" s="33" t="s">
+    <row r="8" spans="1:21" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="38"/>
+      <c r="C8" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="34"/>
-      <c r="E8" s="35" t="s">
+      <c r="D8" s="51"/>
+      <c r="E8" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="35"/>
-      <c r="G8" s="36" t="s">
+      <c r="F8" s="52"/>
+      <c r="G8" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="37" t="s">
+      <c r="H8" s="53"/>
+      <c r="I8" s="53"/>
+      <c r="J8" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="K8" s="38"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="33" t="s">
+      <c r="K8" s="55"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="N8" s="34"/>
-      <c r="O8" s="39"/>
-      <c r="P8" s="39"/>
-      <c r="Q8" s="40" t="s">
+      <c r="N8" s="51"/>
+      <c r="O8" s="56" t="s">
+        <v>47</v>
+      </c>
+      <c r="P8" s="56"/>
+      <c r="Q8" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="R8" s="41"/>
-      <c r="S8" s="42"/>
-      <c r="T8" s="43"/>
-      <c r="U8" s="44"/>
-      <c r="V8" s="31"/>
+      <c r="R8" s="58"/>
+      <c r="S8" s="59"/>
+      <c r="T8" s="60" t="s">
+        <v>48</v>
+      </c>
+      <c r="U8" s="61"/>
     </row>
-    <row r="9" spans="2:22" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="21"/>
-      <c r="C9" s="45" t="s">
+    <row r="9" spans="1:21" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="38"/>
+      <c r="C9" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="46"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="49" t="s">
+      <c r="D9" s="63"/>
+      <c r="E9" s="64" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="65"/>
+      <c r="G9" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="50"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="47"/>
-      <c r="K9" s="52"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="45" t="s">
+      <c r="H9" s="67"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="64" t="s">
+        <v>67</v>
+      </c>
+      <c r="K9" s="69"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="62" t="s">
+        <v>40</v>
+      </c>
+      <c r="N9" s="63"/>
+      <c r="O9" s="70" t="s">
+        <v>49</v>
+      </c>
+      <c r="P9" s="70"/>
+      <c r="Q9" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="R9" s="72"/>
+      <c r="S9" s="40"/>
+      <c r="T9" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="U9" s="73"/>
+    </row>
+    <row r="10" spans="1:21" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="38"/>
+      <c r="C10" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="N9" s="46"/>
-      <c r="O9" s="53"/>
-      <c r="P9" s="53"/>
-      <c r="Q9" s="54" t="s">
+      <c r="D10" s="31"/>
+      <c r="E10" s="99" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="100"/>
+      <c r="G10" s="101" t="s">
         <v>17</v>
       </c>
-      <c r="R9" s="55"/>
-      <c r="S9" s="12"/>
-      <c r="T9" s="18"/>
-      <c r="U9" s="56"/>
-      <c r="V9" s="31"/>
+      <c r="H10" s="102"/>
+      <c r="I10" s="103"/>
+      <c r="J10" s="99" t="s">
+        <v>69</v>
+      </c>
+      <c r="K10" s="104"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="93" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" s="97"/>
+      <c r="O10" s="91" t="s">
+        <v>51</v>
+      </c>
+      <c r="P10" s="98"/>
+      <c r="Q10" s="101" t="s">
+        <v>17</v>
+      </c>
+      <c r="R10" s="102"/>
+      <c r="S10" s="103"/>
+      <c r="T10" s="91" t="s">
+        <v>52</v>
+      </c>
+      <c r="U10" s="92"/>
     </row>
-    <row r="10" spans="2:22" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="21"/>
-      <c r="C10" s="22" t="s">
+    <row r="11" spans="1:21" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="38"/>
+      <c r="C11" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="23"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="59" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" s="60"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="57"/>
-      <c r="K10" s="62"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="63"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="64"/>
-      <c r="P10" s="65"/>
-      <c r="Q10" s="66"/>
-      <c r="R10" s="67"/>
-      <c r="S10" s="67"/>
-      <c r="T10" s="64"/>
-      <c r="U10" s="68"/>
-      <c r="V10" s="69"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="94" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="95"/>
+      <c r="G11" s="95"/>
+      <c r="H11" s="95"/>
+      <c r="I11" s="95"/>
+      <c r="J11" s="95"/>
+      <c r="K11" s="96"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="93" t="s">
+        <v>41</v>
+      </c>
+      <c r="N11" s="97"/>
+      <c r="O11" s="91" t="s">
+        <v>53</v>
+      </c>
+      <c r="P11" s="98"/>
+      <c r="Q11" s="98"/>
+      <c r="R11" s="98"/>
+      <c r="S11" s="98"/>
+      <c r="T11" s="98"/>
+      <c r="U11" s="92"/>
     </row>
-    <row r="11" spans="2:22" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="21"/>
-      <c r="C11" s="63" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="70" t="s">
+    <row r="12" spans="1:21" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="39"/>
+      <c r="C12" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
-      <c r="I11" s="71"/>
-      <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="63"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="64"/>
-      <c r="P11" s="65"/>
-      <c r="Q11" s="65"/>
-      <c r="R11" s="65"/>
-      <c r="S11" s="65"/>
-      <c r="T11" s="65"/>
-      <c r="U11" s="68"/>
-      <c r="V11" s="69"/>
-    </row>
-    <row r="12" spans="2:22" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="73"/>
-      <c r="C12" s="74" t="s">
-        <v>22</v>
-      </c>
       <c r="D12" s="75"/>
-      <c r="E12" s="37"/>
+      <c r="E12" s="54"/>
       <c r="F12" s="76"/>
       <c r="G12" s="76"/>
       <c r="H12" s="76"/>
       <c r="I12" s="76"/>
       <c r="J12" s="76"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="73"/>
-      <c r="M12" s="77"/>
-      <c r="N12" s="42"/>
-      <c r="O12" s="78"/>
-      <c r="P12" s="79"/>
-      <c r="Q12" s="79"/>
-      <c r="R12" s="79"/>
-      <c r="S12" s="79"/>
-      <c r="T12" s="79"/>
-      <c r="U12" s="80"/>
-      <c r="V12" s="69"/>
+      <c r="K12" s="55"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="77" t="s">
+        <v>42</v>
+      </c>
+      <c r="N12" s="78"/>
+      <c r="O12" s="79" t="s">
+        <v>54</v>
+      </c>
+      <c r="P12" s="80"/>
+      <c r="Q12" s="80"/>
+      <c r="R12" s="80"/>
+      <c r="S12" s="80"/>
+      <c r="T12" s="80"/>
+      <c r="U12" s="81"/>
     </row>
-    <row r="13" spans="2:22" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="81" t="s">
+    <row r="13" spans="1:21" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="82" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="83"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="85"/>
+      <c r="F13" s="86"/>
+      <c r="G13" s="86"/>
+      <c r="H13" s="86"/>
+      <c r="I13" s="86"/>
+      <c r="J13" s="86"/>
+      <c r="K13" s="86"/>
+      <c r="L13" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="82"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="85"/>
-      <c r="G13" s="85"/>
-      <c r="H13" s="85"/>
-      <c r="I13" s="85"/>
-      <c r="J13" s="85"/>
-      <c r="K13" s="85"/>
-      <c r="L13" s="86" t="s">
+      <c r="M13" s="88"/>
+      <c r="N13" s="89"/>
+      <c r="O13" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="M13" s="87"/>
-      <c r="N13" s="88"/>
-      <c r="O13" s="84" t="s">
+      <c r="P13" s="86"/>
+      <c r="Q13" s="86"/>
+      <c r="R13" s="86"/>
+      <c r="S13" s="86"/>
+      <c r="T13" s="86"/>
+      <c r="U13" s="90"/>
+    </row>
+    <row r="14" spans="1:21" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
+      <c r="U14" s="9"/>
+    </row>
+    <row r="15" spans="1:21" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="10"/>
+      <c r="B15" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="P13" s="85"/>
-      <c r="Q13" s="85"/>
-      <c r="R13" s="85"/>
-      <c r="S13" s="85"/>
-      <c r="T13" s="85"/>
-      <c r="U13" s="89"/>
-      <c r="V13" s="69"/>
+      <c r="C15" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="105" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="106"/>
+      <c r="G15" s="106"/>
+      <c r="H15" s="106"/>
+      <c r="I15" s="106"/>
+      <c r="J15" s="106"/>
+      <c r="K15" s="107"/>
+      <c r="L15" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15" s="108" t="s">
+        <v>30</v>
+      </c>
+      <c r="N15" s="108"/>
+      <c r="O15" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="P15" s="109"/>
+      <c r="Q15" s="110" t="s">
+        <v>32</v>
+      </c>
+      <c r="R15" s="110"/>
+      <c r="S15" s="110"/>
+      <c r="T15" s="110" t="s">
+        <v>33</v>
+      </c>
+      <c r="U15" s="111"/>
     </row>
-    <row r="14" spans="2:22" ht="21" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="90"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="90"/>
-      <c r="E14" s="90"/>
-      <c r="F14" s="90"/>
-      <c r="G14" s="90"/>
-      <c r="H14" s="90"/>
-      <c r="I14" s="90"/>
-      <c r="J14" s="90"/>
-      <c r="K14" s="90"/>
-      <c r="L14" s="91"/>
-      <c r="M14" s="91"/>
-      <c r="N14" s="92"/>
-      <c r="O14" s="90"/>
-      <c r="P14" s="90"/>
-      <c r="Q14" s="90"/>
-      <c r="R14" s="90"/>
-      <c r="S14" s="90"/>
-      <c r="T14" s="90"/>
-      <c r="U14" s="93"/>
+    <row r="16" spans="1:21" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="14">
+        <v>1</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="112" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="113"/>
+      <c r="G16" s="113"/>
+      <c r="H16" s="113"/>
+      <c r="I16" s="113"/>
+      <c r="J16" s="113"/>
+      <c r="K16" s="114"/>
+      <c r="L16" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M16" s="115" t="s">
+        <v>59</v>
+      </c>
+      <c r="N16" s="116"/>
+      <c r="O16" s="117" t="s">
+        <v>60</v>
+      </c>
+      <c r="P16" s="117"/>
+      <c r="Q16" s="117" t="s">
+        <v>61</v>
+      </c>
+      <c r="R16" s="117"/>
+      <c r="S16" s="117"/>
+      <c r="T16" s="115" t="s">
+        <v>62</v>
+      </c>
+      <c r="U16" s="118"/>
     </row>
-    <row r="15" spans="2:22" s="104" customFormat="1" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="94" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="95" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="95" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="96" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" s="97"/>
-      <c r="G15" s="97"/>
-      <c r="H15" s="97"/>
-      <c r="I15" s="97"/>
-      <c r="J15" s="97"/>
-      <c r="K15" s="98"/>
-      <c r="L15" s="99" t="s">
-        <v>30</v>
-      </c>
-      <c r="M15" s="100" t="s">
-        <v>31</v>
-      </c>
-      <c r="N15" s="100"/>
-      <c r="O15" s="101" t="s">
-        <v>32</v>
-      </c>
-      <c r="P15" s="101"/>
-      <c r="Q15" s="102" t="s">
-        <v>33</v>
-      </c>
-      <c r="R15" s="102"/>
-      <c r="S15" s="102"/>
-      <c r="T15" s="102" t="s">
+    <row r="17" spans="2:21" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="17"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="119"/>
+      <c r="F17" s="120"/>
+      <c r="G17" s="120"/>
+      <c r="H17" s="120"/>
+      <c r="I17" s="120"/>
+      <c r="J17" s="120"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="122"/>
+      <c r="N17" s="123"/>
+      <c r="O17" s="122"/>
+      <c r="P17" s="123"/>
+      <c r="Q17" s="122"/>
+      <c r="R17" s="124"/>
+      <c r="S17" s="123"/>
+      <c r="T17" s="122"/>
+      <c r="U17" s="125"/>
+    </row>
+    <row r="18" spans="2:21" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="17"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="119"/>
+      <c r="F18" s="120"/>
+      <c r="G18" s="120"/>
+      <c r="H18" s="120"/>
+      <c r="I18" s="120"/>
+      <c r="J18" s="120"/>
+      <c r="K18" s="121"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="122"/>
+      <c r="N18" s="123"/>
+      <c r="O18" s="122"/>
+      <c r="P18" s="123"/>
+      <c r="Q18" s="122"/>
+      <c r="R18" s="124"/>
+      <c r="S18" s="123"/>
+      <c r="T18" s="122"/>
+      <c r="U18" s="125"/>
+    </row>
+    <row r="19" spans="2:21" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="17"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="120"/>
+      <c r="G19" s="120"/>
+      <c r="H19" s="120"/>
+      <c r="I19" s="120"/>
+      <c r="J19" s="120"/>
+      <c r="K19" s="121"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="122"/>
+      <c r="N19" s="123"/>
+      <c r="O19" s="122"/>
+      <c r="P19" s="123"/>
+      <c r="Q19" s="122"/>
+      <c r="R19" s="124"/>
+      <c r="S19" s="123"/>
+      <c r="T19" s="122"/>
+      <c r="U19" s="125"/>
+    </row>
+    <row r="20" spans="2:21" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="17"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="119"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="120"/>
+      <c r="I20" s="120"/>
+      <c r="J20" s="120"/>
+      <c r="K20" s="121"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="122"/>
+      <c r="N20" s="123"/>
+      <c r="O20" s="122"/>
+      <c r="P20" s="123"/>
+      <c r="Q20" s="122"/>
+      <c r="R20" s="124"/>
+      <c r="S20" s="123"/>
+      <c r="T20" s="122"/>
+      <c r="U20" s="125"/>
+    </row>
+    <row r="21" spans="2:21" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="17"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="119"/>
+      <c r="F21" s="120"/>
+      <c r="G21" s="120"/>
+      <c r="H21" s="120"/>
+      <c r="I21" s="120"/>
+      <c r="J21" s="120"/>
+      <c r="K21" s="121"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="122"/>
+      <c r="N21" s="123"/>
+      <c r="O21" s="122"/>
+      <c r="P21" s="123"/>
+      <c r="Q21" s="122"/>
+      <c r="R21" s="124"/>
+      <c r="S21" s="123"/>
+      <c r="T21" s="122"/>
+      <c r="U21" s="125"/>
+    </row>
+    <row r="22" spans="2:21" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="17"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="119"/>
+      <c r="F22" s="120"/>
+      <c r="G22" s="120"/>
+      <c r="H22" s="120"/>
+      <c r="I22" s="120"/>
+      <c r="J22" s="120"/>
+      <c r="K22" s="121"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="122"/>
+      <c r="N22" s="123"/>
+      <c r="O22" s="122"/>
+      <c r="P22" s="123"/>
+      <c r="Q22" s="122"/>
+      <c r="R22" s="124"/>
+      <c r="S22" s="123"/>
+      <c r="T22" s="122"/>
+      <c r="U22" s="125"/>
+    </row>
+    <row r="23" spans="2:21" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="17"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="119"/>
+      <c r="F23" s="120"/>
+      <c r="G23" s="120"/>
+      <c r="H23" s="120"/>
+      <c r="I23" s="120"/>
+      <c r="J23" s="120"/>
+      <c r="K23" s="121"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="122"/>
+      <c r="N23" s="123"/>
+      <c r="O23" s="122"/>
+      <c r="P23" s="123"/>
+      <c r="Q23" s="122"/>
+      <c r="R23" s="124"/>
+      <c r="S23" s="123"/>
+      <c r="T23" s="122"/>
+      <c r="U23" s="125"/>
+    </row>
+    <row r="24" spans="2:21" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="17"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="119"/>
+      <c r="F24" s="120"/>
+      <c r="G24" s="120"/>
+      <c r="H24" s="120"/>
+      <c r="I24" s="120"/>
+      <c r="J24" s="120"/>
+      <c r="K24" s="121"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="122"/>
+      <c r="N24" s="123"/>
+      <c r="O24" s="122"/>
+      <c r="P24" s="123"/>
+      <c r="Q24" s="122"/>
+      <c r="R24" s="124"/>
+      <c r="S24" s="123"/>
+      <c r="T24" s="122"/>
+      <c r="U24" s="125"/>
+    </row>
+    <row r="25" spans="2:21" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="17"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="119"/>
+      <c r="F25" s="120"/>
+      <c r="G25" s="120"/>
+      <c r="H25" s="120"/>
+      <c r="I25" s="120"/>
+      <c r="J25" s="120"/>
+      <c r="K25" s="121"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="122"/>
+      <c r="N25" s="123"/>
+      <c r="O25" s="122"/>
+      <c r="P25" s="123"/>
+      <c r="Q25" s="122"/>
+      <c r="R25" s="124"/>
+      <c r="S25" s="123"/>
+      <c r="T25" s="122"/>
+      <c r="U25" s="125"/>
+    </row>
+    <row r="26" spans="2:21" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B26" s="20"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="126"/>
+      <c r="F26" s="127"/>
+      <c r="G26" s="127"/>
+      <c r="H26" s="127"/>
+      <c r="I26" s="127"/>
+      <c r="J26" s="127"/>
+      <c r="K26" s="128"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="129"/>
+      <c r="N26" s="130"/>
+      <c r="O26" s="131"/>
+      <c r="P26" s="131"/>
+      <c r="Q26" s="132"/>
+      <c r="R26" s="133"/>
+      <c r="S26" s="134"/>
+      <c r="T26" s="132"/>
+      <c r="U26" s="135"/>
+    </row>
+    <row r="27" spans="2:21" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="142" t="s">
         <v>34</v>
       </c>
-      <c r="U15" s="103"/>
-      <c r="V15" s="10"/>
+      <c r="C27" s="143"/>
+      <c r="D27" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="144" t="s">
+        <v>63</v>
+      </c>
+      <c r="F27" s="145"/>
+      <c r="G27" s="146" t="s">
+        <v>36</v>
+      </c>
+      <c r="H27" s="143"/>
+      <c r="I27" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="J27" s="144" t="s">
+        <v>64</v>
+      </c>
+      <c r="K27" s="145"/>
+      <c r="L27" s="136" t="s">
+        <v>37</v>
+      </c>
+      <c r="M27" s="138"/>
+      <c r="N27" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="O27" s="144" t="s">
+        <v>65</v>
+      </c>
+      <c r="P27" s="145"/>
+      <c r="Q27" s="136" t="s">
+        <v>38</v>
+      </c>
+      <c r="R27" s="137"/>
+      <c r="S27" s="138"/>
+      <c r="T27" s="139" t="s">
+        <v>39</v>
+      </c>
+      <c r="U27" s="140"/>
     </row>
-    <row r="16" spans="2:22" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="105">
-        <v>1</v>
-      </c>
-      <c r="C16" s="106"/>
-      <c r="D16" s="106"/>
-      <c r="E16" s="107"/>
-      <c r="F16" s="108"/>
-      <c r="G16" s="108"/>
-      <c r="H16" s="108"/>
-      <c r="I16" s="108"/>
-      <c r="J16" s="108"/>
-      <c r="K16" s="109"/>
-      <c r="L16" s="110"/>
-      <c r="M16" s="111"/>
-      <c r="N16" s="112"/>
-      <c r="O16" s="113">
-        <f>M16*L16</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="113"/>
-      <c r="Q16" s="113">
-        <f>O16*10%</f>
-        <v>0</v>
-      </c>
-      <c r="R16" s="113"/>
-      <c r="S16" s="113"/>
-      <c r="T16" s="111"/>
-      <c r="U16" s="114"/>
-    </row>
-    <row r="17" spans="2:22" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="115"/>
-      <c r="C17" s="116"/>
-      <c r="D17" s="116"/>
-      <c r="E17" s="117"/>
-      <c r="F17" s="118"/>
-      <c r="G17" s="118"/>
-      <c r="H17" s="118"/>
-      <c r="I17" s="118"/>
-      <c r="J17" s="118"/>
-      <c r="K17" s="119"/>
-      <c r="L17" s="120"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="122"/>
-      <c r="O17" s="121"/>
-      <c r="P17" s="122"/>
-      <c r="Q17" s="121"/>
-      <c r="R17" s="123"/>
-      <c r="S17" s="122"/>
-      <c r="T17" s="121"/>
-      <c r="U17" s="124"/>
-      <c r="V17" s="125"/>
-    </row>
-    <row r="18" spans="2:22" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="115"/>
-      <c r="C18" s="116"/>
-      <c r="D18" s="116"/>
-      <c r="E18" s="117"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
-      <c r="H18" s="118"/>
-      <c r="I18" s="118"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="119"/>
-      <c r="L18" s="120"/>
-      <c r="M18" s="121"/>
-      <c r="N18" s="122"/>
-      <c r="O18" s="121"/>
-      <c r="P18" s="122"/>
-      <c r="Q18" s="121"/>
-      <c r="R18" s="123"/>
-      <c r="S18" s="122"/>
-      <c r="T18" s="121"/>
-      <c r="U18" s="124"/>
-      <c r="V18" s="125"/>
-    </row>
-    <row r="19" spans="2:22" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="115"/>
-      <c r="C19" s="116"/>
-      <c r="D19" s="116"/>
-      <c r="E19" s="117"/>
-      <c r="F19" s="118"/>
-      <c r="G19" s="118"/>
-      <c r="H19" s="118"/>
-      <c r="I19" s="118"/>
-      <c r="J19" s="118"/>
-      <c r="K19" s="119"/>
-      <c r="L19" s="120"/>
-      <c r="M19" s="121"/>
-      <c r="N19" s="122"/>
-      <c r="O19" s="121"/>
-      <c r="P19" s="122"/>
-      <c r="Q19" s="121"/>
-      <c r="R19" s="123"/>
-      <c r="S19" s="122"/>
-      <c r="T19" s="121"/>
-      <c r="U19" s="124"/>
-      <c r="V19" s="125"/>
-    </row>
-    <row r="20" spans="2:22" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="115"/>
-      <c r="C20" s="116"/>
-      <c r="D20" s="116"/>
-      <c r="E20" s="117"/>
-      <c r="F20" s="118"/>
-      <c r="G20" s="118"/>
-      <c r="H20" s="118"/>
-      <c r="I20" s="118"/>
-      <c r="J20" s="118"/>
-      <c r="K20" s="119"/>
-      <c r="L20" s="120"/>
-      <c r="M20" s="121"/>
-      <c r="N20" s="122"/>
-      <c r="O20" s="121"/>
-      <c r="P20" s="122"/>
-      <c r="Q20" s="121"/>
-      <c r="R20" s="123"/>
-      <c r="S20" s="122"/>
-      <c r="T20" s="121"/>
-      <c r="U20" s="124"/>
-      <c r="V20" s="125"/>
-    </row>
-    <row r="21" spans="2:22" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="115"/>
-      <c r="C21" s="116"/>
-      <c r="D21" s="116"/>
-      <c r="E21" s="117"/>
-      <c r="F21" s="118"/>
-      <c r="G21" s="118"/>
-      <c r="H21" s="118"/>
-      <c r="I21" s="118"/>
-      <c r="J21" s="118"/>
-      <c r="K21" s="119"/>
-      <c r="L21" s="120"/>
-      <c r="M21" s="121"/>
-      <c r="N21" s="122"/>
-      <c r="O21" s="121"/>
-      <c r="P21" s="122"/>
-      <c r="Q21" s="121"/>
-      <c r="R21" s="123"/>
-      <c r="S21" s="122"/>
-      <c r="T21" s="121"/>
-      <c r="U21" s="124"/>
-      <c r="V21" s="125"/>
-    </row>
-    <row r="22" spans="2:22" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="115"/>
-      <c r="C22" s="116"/>
-      <c r="D22" s="116"/>
-      <c r="E22" s="117"/>
-      <c r="F22" s="118"/>
-      <c r="G22" s="118"/>
-      <c r="H22" s="118"/>
-      <c r="I22" s="118"/>
-      <c r="J22" s="118"/>
-      <c r="K22" s="119"/>
-      <c r="L22" s="120"/>
-      <c r="M22" s="121"/>
-      <c r="N22" s="122"/>
-      <c r="O22" s="121"/>
-      <c r="P22" s="122"/>
-      <c r="Q22" s="121"/>
-      <c r="R22" s="123"/>
-      <c r="S22" s="122"/>
-      <c r="T22" s="121"/>
-      <c r="U22" s="124"/>
-      <c r="V22" s="125"/>
-    </row>
-    <row r="23" spans="2:22" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="115"/>
-      <c r="C23" s="116"/>
-      <c r="D23" s="116"/>
-      <c r="E23" s="117"/>
-      <c r="F23" s="118"/>
-      <c r="G23" s="118"/>
-      <c r="H23" s="118"/>
-      <c r="I23" s="118"/>
-      <c r="J23" s="118"/>
-      <c r="K23" s="119"/>
-      <c r="L23" s="120"/>
-      <c r="M23" s="121"/>
-      <c r="N23" s="122"/>
-      <c r="O23" s="121"/>
-      <c r="P23" s="122"/>
-      <c r="Q23" s="121"/>
-      <c r="R23" s="123"/>
-      <c r="S23" s="122"/>
-      <c r="T23" s="121"/>
-      <c r="U23" s="124"/>
-      <c r="V23" s="125"/>
-    </row>
-    <row r="24" spans="2:22" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="115"/>
-      <c r="C24" s="116"/>
-      <c r="D24" s="116"/>
-      <c r="E24" s="117"/>
-      <c r="F24" s="118"/>
-      <c r="G24" s="118"/>
-      <c r="H24" s="118"/>
-      <c r="I24" s="118"/>
-      <c r="J24" s="118"/>
-      <c r="K24" s="119"/>
-      <c r="L24" s="120"/>
-      <c r="M24" s="121"/>
-      <c r="N24" s="122"/>
-      <c r="O24" s="121"/>
-      <c r="P24" s="122"/>
-      <c r="Q24" s="121"/>
-      <c r="R24" s="123"/>
-      <c r="S24" s="122"/>
-      <c r="T24" s="121"/>
-      <c r="U24" s="124"/>
-      <c r="V24" s="125"/>
-    </row>
-    <row r="25" spans="2:22" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="115"/>
-      <c r="C25" s="116"/>
-      <c r="D25" s="116"/>
-      <c r="E25" s="117"/>
-      <c r="F25" s="118"/>
-      <c r="G25" s="118"/>
-      <c r="H25" s="118"/>
-      <c r="I25" s="118"/>
-      <c r="J25" s="118"/>
-      <c r="K25" s="119"/>
-      <c r="L25" s="120"/>
-      <c r="M25" s="121"/>
-      <c r="N25" s="122"/>
-      <c r="O25" s="121"/>
-      <c r="P25" s="122"/>
-      <c r="Q25" s="121"/>
-      <c r="R25" s="123"/>
-      <c r="S25" s="122"/>
-      <c r="T25" s="121"/>
-      <c r="U25" s="124"/>
-      <c r="V25" s="125"/>
-    </row>
-    <row r="26" spans="2:22" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B26" s="126"/>
-      <c r="C26" s="127"/>
-      <c r="D26" s="127"/>
-      <c r="E26" s="128"/>
-      <c r="F26" s="129"/>
-      <c r="G26" s="129"/>
-      <c r="H26" s="129"/>
-      <c r="I26" s="129"/>
-      <c r="J26" s="129"/>
-      <c r="K26" s="130"/>
-      <c r="L26" s="131"/>
-      <c r="M26" s="132"/>
-      <c r="N26" s="133"/>
-      <c r="O26" s="134"/>
-      <c r="P26" s="134"/>
-      <c r="Q26" s="135"/>
-      <c r="R26" s="136"/>
-      <c r="S26" s="137"/>
-      <c r="T26" s="135"/>
-      <c r="U26" s="138"/>
-      <c r="V26" s="139"/>
-    </row>
-    <row r="27" spans="2:22" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="140" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="141"/>
-      <c r="D27" s="142" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="143">
-        <f>SUM(O16:P26)</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="144"/>
-      <c r="G27" s="145" t="s">
-        <v>37</v>
-      </c>
-      <c r="H27" s="141"/>
-      <c r="I27" s="146" t="s">
-        <v>36</v>
-      </c>
-      <c r="J27" s="143">
-        <f>E27*10%</f>
-        <v>0</v>
-      </c>
-      <c r="K27" s="144"/>
-      <c r="L27" s="147" t="s">
-        <v>38</v>
-      </c>
-      <c r="M27" s="148"/>
-      <c r="N27" s="149" t="s">
-        <v>36</v>
-      </c>
-      <c r="O27" s="143">
-        <f>E27+J27</f>
-        <v>0</v>
-      </c>
-      <c r="P27" s="144"/>
-      <c r="Q27" s="147" t="s">
-        <v>39</v>
-      </c>
-      <c r="R27" s="150"/>
-      <c r="S27" s="148"/>
-      <c r="T27" s="151" t="s">
-        <v>40</v>
-      </c>
-      <c r="U27" s="152"/>
-      <c r="V27" s="153"/>
-    </row>
-    <row r="28" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="154"/>
-      <c r="C28" s="154"/>
-      <c r="D28" s="154"/>
-      <c r="E28" s="154"/>
-      <c r="F28" s="154"/>
-      <c r="G28" s="154"/>
-      <c r="H28" s="154"/>
-      <c r="I28" s="154"/>
-      <c r="J28" s="154"/>
-      <c r="K28" s="154"/>
-      <c r="L28" s="154"/>
-      <c r="M28" s="154"/>
-      <c r="N28" s="154"/>
-      <c r="O28" s="154"/>
-      <c r="P28" s="154"/>
-      <c r="Q28" s="154"/>
-      <c r="R28" s="154"/>
-      <c r="S28" s="154"/>
-      <c r="T28" s="154"/>
-      <c r="U28" s="154"/>
-      <c r="V28" s="155"/>
+    <row r="28" spans="2:21" ht="24" x14ac:dyDescent="0.3">
+      <c r="B28" s="141"/>
+      <c r="C28" s="141"/>
+      <c r="D28" s="141"/>
+      <c r="E28" s="141"/>
+      <c r="F28" s="141"/>
+      <c r="G28" s="141"/>
+      <c r="H28" s="141"/>
+      <c r="I28" s="141"/>
+      <c r="J28" s="141"/>
+      <c r="K28" s="141"/>
+      <c r="L28" s="141"/>
+      <c r="M28" s="141"/>
+      <c r="N28" s="141"/>
+      <c r="O28" s="141"/>
+      <c r="P28" s="141"/>
+      <c r="Q28" s="141"/>
+      <c r="R28" s="141"/>
+      <c r="S28" s="141"/>
+      <c r="T28" s="141"/>
+      <c r="U28" s="141"/>
     </row>
   </sheetData>
   <mergeCells count="125">
@@ -3172,6 +3276,8 @@
     <mergeCell ref="J10:K10"/>
     <mergeCell ref="M10:N10"/>
     <mergeCell ref="O10:P10"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="O8:P8"/>
     <mergeCell ref="Q8:S8"/>
     <mergeCell ref="T8:U8"/>
     <mergeCell ref="C9:D9"/>
@@ -3182,16 +3288,6 @@
     <mergeCell ref="O9:P9"/>
     <mergeCell ref="Q9:S9"/>
     <mergeCell ref="T9:U9"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:K7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="O7:U7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="O8:P8"/>
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="M6:N6"/>
@@ -3208,11 +3304,17 @@
     <mergeCell ref="O5:U5"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:K7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="O7:U7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:K8"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0" right="0" top="0" bottom="3.1496062992125986" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="47" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>